--- a/backend/data/financials_by_company/0183.HK.xlsx
+++ b/backend/data/financials_by_company/0183.HK.xlsx
@@ -667,572 +667,572 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>-11230230</v>
+        <v>-5148825</v>
       </c>
       <c r="C2" t="n">
         <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>-161194000</v>
+        <v>70585000</v>
       </c>
       <c r="E2" t="n">
-        <v>-68062000</v>
+        <v>-31205000</v>
       </c>
       <c r="F2" t="n">
-        <v>-68062000</v>
+        <v>-31205000</v>
       </c>
       <c r="G2" t="n">
-        <v>-241948000</v>
+        <v>36139000</v>
       </c>
       <c r="H2" t="n">
-        <v>4219000</v>
+        <v>4566000</v>
       </c>
       <c r="I2" t="n">
-        <v>12086000</v>
+        <v>6260000</v>
       </c>
       <c r="J2" t="n">
-        <v>-229256000</v>
+        <v>39380000</v>
       </c>
       <c r="K2" t="n">
-        <v>-233475000</v>
+        <v>34814000</v>
       </c>
       <c r="L2" t="n">
-        <v>4144000</v>
+        <v>9574000</v>
       </c>
       <c r="M2" t="n">
-        <v>8470000</v>
+        <v>2829000</v>
       </c>
       <c r="N2" t="n">
-        <v>12614000</v>
+        <v>12403000</v>
       </c>
       <c r="O2" t="n">
-        <v>-185116230</v>
+        <v>62195175</v>
       </c>
       <c r="P2" t="n">
-        <v>-241948000</v>
+        <v>36139000</v>
       </c>
       <c r="Q2" t="n">
-        <v>47711000</v>
+        <v>39369000</v>
       </c>
       <c r="R2" t="n">
-        <v>566913000</v>
+        <v>561202000</v>
       </c>
       <c r="S2" t="n">
-        <v>566913000</v>
+        <v>559300000</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4268</v>
+        <v>0.0644</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4268</v>
+        <v>0.0646</v>
       </c>
       <c r="V2" t="n">
-        <v>-241948000</v>
+        <v>36139000</v>
       </c>
       <c r="W2" t="n">
-        <v>-241948000</v>
+        <v>36139000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-241948000</v>
+        <v>36139000</v>
       </c>
       <c r="Z2" t="n">
-        <v>213000</v>
+        <v>52000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-242161000</v>
+        <v>36087000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-242161000</v>
+        <v>36087000</v>
       </c>
       <c r="AC2" t="n">
-        <v>216000</v>
+        <v>-4102000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-241945000</v>
+        <v>31985000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4937000</v>
+        <v>2739000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-60236000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-216000</v>
-      </c>
+        <v>2633000</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>25249000</v>
+        <v>-2633000</v>
       </c>
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="n">
-        <v>4144000</v>
+        <v>9574000</v>
       </c>
       <c r="AK2" t="n">
-        <v>8470000</v>
+        <v>2829000</v>
       </c>
       <c r="AL2" t="n">
-        <v>12614000</v>
+        <v>12403000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-6593000</v>
+        <v>-12610000</v>
       </c>
       <c r="AN2" t="n">
-        <v>35625000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>10743000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>4219000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4219000</v>
-      </c>
+        <v>33109000</v>
+      </c>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
       <c r="AR2" t="n">
-        <v>3584000</v>
+        <v>33514000</v>
       </c>
       <c r="AS2" t="n">
-        <v>3584000</v>
+        <v>33514000</v>
       </c>
       <c r="AT2" t="n">
-        <v>29032000</v>
+        <v>20499000</v>
       </c>
       <c r="AU2" t="n">
-        <v>12086000</v>
+        <v>6260000</v>
       </c>
       <c r="AV2" t="n">
-        <v>41118000</v>
+        <v>26759000</v>
       </c>
       <c r="AW2" t="n">
-        <v>41118000</v>
+        <v>26759000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-1466432.864229</v>
+        <v>-128444.5118</v>
       </c>
       <c r="C3" t="n">
-        <v>0.026719</v>
+        <v>0.006891</v>
       </c>
       <c r="D3" t="n">
-        <v>-4105000</v>
+        <v>-117904000</v>
       </c>
       <c r="E3" t="n">
-        <v>-54884000</v>
+        <v>-18639000</v>
       </c>
       <c r="F3" t="n">
-        <v>-54884000</v>
+        <v>-18639000</v>
       </c>
       <c r="G3" t="n">
-        <v>-67611000</v>
+        <v>-144050000</v>
       </c>
       <c r="H3" t="n">
-        <v>4311000</v>
+        <v>4614000</v>
       </c>
       <c r="I3" t="n">
-        <v>11545000</v>
+        <v>6749000</v>
       </c>
       <c r="J3" t="n">
-        <v>-58989000</v>
+        <v>-136543000</v>
       </c>
       <c r="K3" t="n">
-        <v>-63300000</v>
+        <v>-141157000</v>
       </c>
       <c r="L3" t="n">
-        <v>4086000</v>
+        <v>-631000</v>
       </c>
       <c r="M3" t="n">
-        <v>6052000</v>
+        <v>2360000</v>
       </c>
       <c r="N3" t="n">
-        <v>10138000</v>
+        <v>1729000</v>
       </c>
       <c r="O3" t="n">
-        <v>-14193432.864229</v>
+        <v>-125539444.5118</v>
       </c>
       <c r="P3" t="n">
-        <v>-67611000</v>
+        <v>-144050000</v>
       </c>
       <c r="Q3" t="n">
-        <v>41909000</v>
+        <v>49816000</v>
       </c>
       <c r="R3" t="n">
-        <v>566812000</v>
+        <v>560813000</v>
       </c>
       <c r="S3" t="n">
-        <v>566812000</v>
+        <v>560813000</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1193</v>
+        <v>-0.2569</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1193</v>
+        <v>-0.2569</v>
       </c>
       <c r="V3" t="n">
-        <v>-67611000</v>
+        <v>-144050000</v>
       </c>
       <c r="W3" t="n">
-        <v>-67611000</v>
+        <v>-144050000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-67611000</v>
+        <v>-144050000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-112000</v>
+        <v>-1522000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-67499000</v>
+        <v>-142528000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-67499000</v>
+        <v>-142528000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1853000</v>
+        <v>-989000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-69352000</v>
+        <v>-143517000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-4138000</v>
+        <v>2718000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-2703000</v>
+        <v>-888000</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>3259000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>-556000</v>
-      </c>
+        <v>888000</v>
+      </c>
+      <c r="AI3" t="inlineStr"/>
       <c r="AJ3" t="n">
-        <v>4086000</v>
+        <v>-631000</v>
       </c>
       <c r="AK3" t="n">
-        <v>6052000</v>
+        <v>2360000</v>
       </c>
       <c r="AL3" t="n">
-        <v>10138000</v>
+        <v>1729000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-3880000</v>
+        <v>-16463000</v>
       </c>
       <c r="AN3" t="n">
-        <v>30364000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>4876000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>4311000</v>
-      </c>
+        <v>43067000</v>
+      </c>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr"/>
       <c r="AR3" t="n">
-        <v>3472000</v>
+        <v>43203000</v>
       </c>
       <c r="AS3" t="n">
-        <v>3472000</v>
+        <v>43203000</v>
       </c>
       <c r="AT3" t="n">
-        <v>26484000</v>
+        <v>26604000</v>
       </c>
       <c r="AU3" t="n">
-        <v>11545000</v>
+        <v>6749000</v>
       </c>
       <c r="AV3" t="n">
-        <v>38029000</v>
+        <v>33353000</v>
       </c>
       <c r="AW3" t="n">
-        <v>38029000</v>
+        <v>33353000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>-128444.5118</v>
+        <v>-1466432.864229</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006891</v>
+        <v>0.026719</v>
       </c>
       <c r="D4" t="n">
-        <v>-117904000</v>
+        <v>-4105000</v>
       </c>
       <c r="E4" t="n">
-        <v>-18639000</v>
+        <v>-54884000</v>
       </c>
       <c r="F4" t="n">
-        <v>-18639000</v>
+        <v>-54884000</v>
       </c>
       <c r="G4" t="n">
-        <v>-144050000</v>
+        <v>-67611000</v>
       </c>
       <c r="H4" t="n">
-        <v>4614000</v>
+        <v>4311000</v>
       </c>
       <c r="I4" t="n">
-        <v>6749000</v>
+        <v>11545000</v>
       </c>
       <c r="J4" t="n">
-        <v>-136543000</v>
+        <v>-58989000</v>
       </c>
       <c r="K4" t="n">
-        <v>-141157000</v>
+        <v>-63300000</v>
       </c>
       <c r="L4" t="n">
-        <v>-631000</v>
+        <v>4086000</v>
       </c>
       <c r="M4" t="n">
-        <v>2360000</v>
+        <v>6052000</v>
       </c>
       <c r="N4" t="n">
-        <v>1729000</v>
+        <v>10138000</v>
       </c>
       <c r="O4" t="n">
-        <v>-125539444.5118</v>
+        <v>-14193432.864229</v>
       </c>
       <c r="P4" t="n">
-        <v>-144050000</v>
+        <v>-67611000</v>
       </c>
       <c r="Q4" t="n">
-        <v>49816000</v>
+        <v>41909000</v>
       </c>
       <c r="R4" t="n">
-        <v>560813000</v>
+        <v>566812000</v>
       </c>
       <c r="S4" t="n">
-        <v>560813000</v>
+        <v>566812000</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2569</v>
+        <v>-0.1193</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2569</v>
+        <v>-0.1193</v>
       </c>
       <c r="V4" t="n">
-        <v>-144050000</v>
+        <v>-67611000</v>
       </c>
       <c r="W4" t="n">
-        <v>-144050000</v>
+        <v>-67611000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-144050000</v>
+        <v>-67611000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-1522000</v>
+        <v>-112000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-142528000</v>
+        <v>-67499000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-142528000</v>
+        <v>-67499000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-989000</v>
+        <v>-1853000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-143517000</v>
+        <v>-69352000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2718000</v>
+        <v>-4138000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-888000</v>
+        <v>-2703000</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>888000</v>
-      </c>
-      <c r="AI4" t="inlineStr"/>
+        <v>3259000</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>-556000</v>
+      </c>
       <c r="AJ4" t="n">
-        <v>-631000</v>
+        <v>4086000</v>
       </c>
       <c r="AK4" t="n">
-        <v>2360000</v>
+        <v>6052000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1729000</v>
+        <v>10138000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-16463000</v>
+        <v>-3880000</v>
       </c>
       <c r="AN4" t="n">
-        <v>43067000</v>
-      </c>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
+        <v>30364000</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4876000</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4311000</v>
+      </c>
       <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>43203000</v>
+        <v>3472000</v>
       </c>
       <c r="AS4" t="n">
-        <v>43203000</v>
+        <v>3472000</v>
       </c>
       <c r="AT4" t="n">
-        <v>26604000</v>
+        <v>26484000</v>
       </c>
       <c r="AU4" t="n">
-        <v>6749000</v>
+        <v>11545000</v>
       </c>
       <c r="AV4" t="n">
-        <v>33353000</v>
+        <v>38029000</v>
       </c>
       <c r="AW4" t="n">
-        <v>33353000</v>
+        <v>38029000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-5148825</v>
+        <v>-11230230</v>
       </c>
       <c r="C5" t="n">
         <v>0.165</v>
       </c>
       <c r="D5" t="n">
-        <v>70585000</v>
+        <v>-161194000</v>
       </c>
       <c r="E5" t="n">
-        <v>-31205000</v>
+        <v>-68062000</v>
       </c>
       <c r="F5" t="n">
-        <v>-31205000</v>
+        <v>-68062000</v>
       </c>
       <c r="G5" t="n">
-        <v>36139000</v>
+        <v>-241948000</v>
       </c>
       <c r="H5" t="n">
-        <v>4566000</v>
+        <v>4219000</v>
       </c>
       <c r="I5" t="n">
-        <v>6260000</v>
+        <v>12086000</v>
       </c>
       <c r="J5" t="n">
-        <v>39380000</v>
+        <v>-229256000</v>
       </c>
       <c r="K5" t="n">
-        <v>34814000</v>
+        <v>-233475000</v>
       </c>
       <c r="L5" t="n">
-        <v>9574000</v>
+        <v>4144000</v>
       </c>
       <c r="M5" t="n">
-        <v>2829000</v>
+        <v>8470000</v>
       </c>
       <c r="N5" t="n">
-        <v>12403000</v>
+        <v>12614000</v>
       </c>
       <c r="O5" t="n">
-        <v>62195175</v>
+        <v>-185116230</v>
       </c>
       <c r="P5" t="n">
-        <v>36139000</v>
+        <v>-241948000</v>
       </c>
       <c r="Q5" t="n">
-        <v>39369000</v>
+        <v>47711000</v>
       </c>
       <c r="R5" t="n">
-        <v>561202000</v>
+        <v>566913000</v>
       </c>
       <c r="S5" t="n">
-        <v>559300000</v>
+        <v>566913000</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0644</v>
+        <v>-0.4268</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0646</v>
+        <v>-0.4268</v>
       </c>
       <c r="V5" t="n">
-        <v>36139000</v>
+        <v>-241948000</v>
       </c>
       <c r="W5" t="n">
-        <v>36139000</v>
+        <v>-241948000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>36139000</v>
+        <v>-241948000</v>
       </c>
       <c r="Z5" t="n">
-        <v>52000</v>
+        <v>213000</v>
       </c>
       <c r="AA5" t="n">
-        <v>36087000</v>
+        <v>-242161000</v>
       </c>
       <c r="AB5" t="n">
-        <v>36087000</v>
+        <v>-242161000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4102000</v>
+        <v>216000</v>
       </c>
       <c r="AD5" t="n">
-        <v>31985000</v>
+        <v>-241945000</v>
       </c>
       <c r="AE5" t="n">
-        <v>2739000</v>
+        <v>-4937000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2633000</v>
-      </c>
-      <c r="AG5" t="inlineStr"/>
+        <v>-60236000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>-216000</v>
+      </c>
       <c r="AH5" t="n">
-        <v>-2633000</v>
+        <v>25249000</v>
       </c>
       <c r="AI5" t="inlineStr"/>
       <c r="AJ5" t="n">
-        <v>9574000</v>
+        <v>4144000</v>
       </c>
       <c r="AK5" t="n">
-        <v>2829000</v>
+        <v>8470000</v>
       </c>
       <c r="AL5" t="n">
-        <v>12403000</v>
+        <v>12614000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-12610000</v>
+        <v>-6593000</v>
       </c>
       <c r="AN5" t="n">
-        <v>33109000</v>
-      </c>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
+        <v>35625000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>10743000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>4219000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>4219000</v>
+      </c>
       <c r="AR5" t="n">
-        <v>33514000</v>
+        <v>3584000</v>
       </c>
       <c r="AS5" t="n">
-        <v>33514000</v>
+        <v>3584000</v>
       </c>
       <c r="AT5" t="n">
-        <v>20499000</v>
+        <v>29032000</v>
       </c>
       <c r="AU5" t="n">
-        <v>6260000</v>
+        <v>12086000</v>
       </c>
       <c r="AV5" t="n">
-        <v>26759000</v>
+        <v>41118000</v>
       </c>
       <c r="AW5" t="n">
-        <v>26759000</v>
+        <v>41118000</v>
       </c>
     </row>
   </sheetData>
@@ -1563,299 +1563,299 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>566912566</v>
+        <v>560813000</v>
       </c>
       <c r="C2" t="n">
-        <v>566912566</v>
+        <v>560813000</v>
       </c>
       <c r="D2" t="n">
-        <v>62450000</v>
+        <v>51528000</v>
       </c>
       <c r="E2" t="n">
-        <v>292593000</v>
+        <v>234707000</v>
       </c>
       <c r="F2" t="n">
-        <v>1384245000</v>
+        <v>1844355000</v>
       </c>
       <c r="G2" t="n">
-        <v>1679147000</v>
+        <v>2080504000</v>
       </c>
       <c r="H2" t="n">
-        <v>120600000</v>
+        <v>275629000</v>
       </c>
       <c r="I2" t="n">
-        <v>1384245000</v>
+        <v>1844355000</v>
       </c>
       <c r="J2" t="n">
-        <v>1386554000</v>
+        <v>1845797000</v>
       </c>
       <c r="K2" t="n">
-        <v>1387024000</v>
+        <v>1857833000</v>
       </c>
       <c r="L2" t="n">
-        <v>1385915000</v>
+        <v>1842469000</v>
       </c>
       <c r="M2" t="n">
-        <v>-639000</v>
+        <v>-3328000</v>
       </c>
       <c r="N2" t="n">
-        <v>1386554000</v>
+        <v>1845797000</v>
       </c>
       <c r="O2" t="n">
-        <v>11202000</v>
+        <v>11867000</v>
       </c>
       <c r="P2" t="n">
-        <v>-248618000</v>
+        <v>195856000</v>
       </c>
       <c r="Q2" t="n">
-        <v>1572570000</v>
+        <v>1570851000</v>
       </c>
       <c r="R2" t="n">
-        <v>56691000</v>
+        <v>56081000</v>
       </c>
       <c r="S2" t="n">
-        <v>56691000</v>
+        <v>56081000</v>
       </c>
       <c r="T2" t="n">
-        <v>331153000</v>
+        <v>294614000</v>
       </c>
       <c r="U2" t="n">
-        <v>5716000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1656000</v>
-      </c>
+        <v>17211000</v>
+      </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>3590000</v>
+        <v>5175000</v>
       </c>
       <c r="X2" t="n">
-        <v>470000</v>
+        <v>12036000</v>
       </c>
       <c r="Y2" t="n">
-        <v>470000</v>
+        <v>12036000</v>
       </c>
       <c r="Z2" t="n">
-        <v>325437000</v>
+        <v>277403000</v>
       </c>
       <c r="AA2" t="n">
-        <v>23968000</v>
+        <v>24841000</v>
       </c>
       <c r="AB2" t="n">
-        <v>292123000</v>
+        <v>222671000</v>
       </c>
       <c r="AC2" t="n">
-        <v>292123000</v>
+        <v>222671000</v>
       </c>
       <c r="AD2" t="n">
-        <v>26280000</v>
+        <v>18231000</v>
       </c>
       <c r="AE2" t="n">
-        <v>2312000</v>
+        <v>18231000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1717068000</v>
+        <v>2137083000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1271031000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>7775000</v>
-      </c>
+        <v>1584051000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>471139000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
+        <v>443784000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>5373000</v>
+      </c>
       <c r="AK2" t="n">
-        <v>106924000</v>
+        <v>71981000</v>
       </c>
       <c r="AL2" t="n">
-        <v>364215000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
+        <v>366430000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
       <c r="AO2" t="n">
-        <v>670728000</v>
+        <v>976946000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2309000</v>
+        <v>1442000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2309000</v>
+        <v>1442000</v>
       </c>
       <c r="AR2" t="n">
-        <v>99389000</v>
+        <v>161707000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-30459000</v>
+        <v>-17811000</v>
       </c>
       <c r="AT2" t="n">
-        <v>129848000</v>
-      </c>
-      <c r="AU2" t="inlineStr"/>
+        <v>179518000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>16249000</v>
+      </c>
       <c r="AV2" t="n">
-        <v>6402000</v>
+        <v>3572000</v>
       </c>
       <c r="AW2" t="n">
-        <v>4223000</v>
+        <v>4306000</v>
       </c>
       <c r="AX2" t="n">
-        <v>119223000</v>
+        <v>155391000</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>446037000</v>
+        <v>553032000</v>
       </c>
       <c r="BA2" t="n">
-        <v>106080000</v>
-      </c>
-      <c r="BB2" t="inlineStr"/>
+        <v>201514000</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>6647000</v>
+      </c>
       <c r="BC2" t="n">
-        <v>63910000</v>
+        <v>104894000</v>
       </c>
       <c r="BD2" t="n">
-        <v>63910000</v>
+        <v>104894000</v>
       </c>
       <c r="BE2" t="n">
-        <v>21616000</v>
+        <v>23962000</v>
       </c>
       <c r="BF2" t="n">
-        <v>2219000</v>
+        <v>1121000</v>
       </c>
       <c r="BG2" t="n">
-        <v>252212000</v>
+        <v>221541000</v>
       </c>
       <c r="BH2" t="n">
-        <v>22069000</v>
+        <v>38362000</v>
       </c>
       <c r="BI2" t="n">
-        <v>230143000</v>
+        <v>183179000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>210269000</v>
+        <v>99939000</v>
       </c>
       <c r="BK2" t="n">
-        <v>19874000</v>
+        <v>83240000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>566912566</v>
+        <v>560813000</v>
       </c>
       <c r="C3" t="n">
-        <v>566912566</v>
+        <v>560813000</v>
       </c>
       <c r="D3" t="n">
-        <v>39918000</v>
+        <v>8068000</v>
       </c>
       <c r="E3" t="n">
-        <v>184250000</v>
+        <v>220632000</v>
       </c>
       <c r="F3" t="n">
-        <v>1616025000</v>
+        <v>1683732000</v>
       </c>
       <c r="G3" t="n">
-        <v>1801619000</v>
+        <v>1906757000</v>
       </c>
       <c r="H3" t="n">
-        <v>148316000</v>
+        <v>238398000</v>
       </c>
       <c r="I3" t="n">
-        <v>1616025000</v>
+        <v>1683732000</v>
       </c>
       <c r="J3" t="n">
-        <v>1617369000</v>
+        <v>1686125000</v>
       </c>
       <c r="K3" t="n">
-        <v>1618308000</v>
+        <v>1687482000</v>
       </c>
       <c r="L3" t="n">
-        <v>1616943000</v>
+        <v>1685587000</v>
       </c>
       <c r="M3" t="n">
-        <v>-426000</v>
+        <v>-538000</v>
       </c>
       <c r="N3" t="n">
-        <v>1617369000</v>
+        <v>1686125000</v>
       </c>
       <c r="O3" t="n">
-        <v>11405000</v>
+        <v>12302000</v>
       </c>
       <c r="P3" t="n">
-        <v>-6916000</v>
+        <v>59980000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1572570000</v>
+        <v>1570851000</v>
       </c>
       <c r="R3" t="n">
-        <v>56691000</v>
+        <v>56081000</v>
       </c>
       <c r="S3" t="n">
-        <v>56691000</v>
+        <v>56081000</v>
       </c>
       <c r="T3" t="n">
-        <v>222292000</v>
+        <v>273482000</v>
       </c>
       <c r="U3" t="n">
-        <v>7565000</v>
+        <v>8461000</v>
       </c>
       <c r="V3" t="n">
-        <v>3252000</v>
+        <v>1929000</v>
       </c>
       <c r="W3" t="n">
-        <v>3374000</v>
+        <v>5175000</v>
       </c>
       <c r="X3" t="n">
-        <v>939000</v>
+        <v>1357000</v>
       </c>
       <c r="Y3" t="n">
-        <v>939000</v>
+        <v>1357000</v>
       </c>
       <c r="Z3" t="n">
-        <v>214727000</v>
+        <v>265021000</v>
       </c>
       <c r="AA3" t="n">
-        <v>23968000</v>
+        <v>23569000</v>
       </c>
       <c r="AB3" t="n">
-        <v>183311000</v>
+        <v>219275000</v>
       </c>
       <c r="AC3" t="n">
-        <v>183311000</v>
+        <v>219275000</v>
       </c>
       <c r="AD3" t="n">
-        <v>2312000</v>
+        <v>2160000</v>
       </c>
       <c r="AE3" t="n">
-        <v>2312000</v>
+        <v>2160000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1839235000</v>
+        <v>1959069000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1476192000</v>
+        <v>1455650000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>462449000</v>
-      </c>
-      <c r="AJ3" t="inlineStr"/>
+        <v>439975000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
       <c r="AK3" t="n">
-        <v>111878000</v>
+        <v>37604000</v>
       </c>
       <c r="AL3" t="n">
-        <v>350571000</v>
+        <v>402371000</v>
       </c>
       <c r="AM3" t="n">
         <v>0</v>
@@ -1864,26 +1864,28 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>837359000</v>
+        <v>865873000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1344000</v>
+        <v>2393000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1344000</v>
+        <v>2393000</v>
       </c>
       <c r="AR3" t="n">
-        <v>138467000</v>
+        <v>140844000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-26736000</v>
+        <v>-22425000</v>
       </c>
       <c r="AT3" t="n">
-        <v>165203000</v>
-      </c>
-      <c r="AU3" t="inlineStr"/>
+        <v>163269000</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
       <c r="AV3" t="n">
-        <v>5506000</v>
+        <v>3572000</v>
       </c>
       <c r="AW3" t="n">
         <v>4306000</v>
@@ -1895,152 +1897,152 @@
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>363043000</v>
+        <v>503419000</v>
       </c>
       <c r="BA3" t="n">
-        <v>108205000</v>
-      </c>
-      <c r="BB3" t="inlineStr"/>
+        <v>164480000</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>8305000</v>
+      </c>
       <c r="BC3" t="n">
-        <v>96980000</v>
+        <v>106485000</v>
       </c>
       <c r="BD3" t="n">
-        <v>96980000</v>
+        <v>106485000</v>
       </c>
       <c r="BE3" t="n">
-        <v>3897000</v>
+        <v>8305000</v>
       </c>
       <c r="BF3" t="n">
-        <v>1624000</v>
+        <v>1603000</v>
       </c>
       <c r="BG3" t="n">
-        <v>152337000</v>
+        <v>222546000</v>
       </c>
       <c r="BH3" t="n">
-        <v>8005000</v>
+        <v>9982000</v>
       </c>
       <c r="BI3" t="n">
-        <v>144332000</v>
+        <v>212564000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>129633000</v>
+        <v>134763000</v>
       </c>
       <c r="BK3" t="n">
-        <v>14699000</v>
+        <v>77801000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>560813000</v>
+        <v>566912566</v>
       </c>
       <c r="C4" t="n">
-        <v>560813000</v>
+        <v>566912566</v>
       </c>
       <c r="D4" t="n">
-        <v>8068000</v>
+        <v>39918000</v>
       </c>
       <c r="E4" t="n">
-        <v>220632000</v>
+        <v>184250000</v>
       </c>
       <c r="F4" t="n">
-        <v>1683732000</v>
+        <v>1616025000</v>
       </c>
       <c r="G4" t="n">
-        <v>1906757000</v>
+        <v>1801619000</v>
       </c>
       <c r="H4" t="n">
-        <v>238398000</v>
+        <v>148316000</v>
       </c>
       <c r="I4" t="n">
-        <v>1683732000</v>
+        <v>1616025000</v>
       </c>
       <c r="J4" t="n">
-        <v>1686125000</v>
+        <v>1617369000</v>
       </c>
       <c r="K4" t="n">
-        <v>1687482000</v>
+        <v>1618308000</v>
       </c>
       <c r="L4" t="n">
-        <v>1685587000</v>
+        <v>1616943000</v>
       </c>
       <c r="M4" t="n">
-        <v>-538000</v>
+        <v>-426000</v>
       </c>
       <c r="N4" t="n">
-        <v>1686125000</v>
+        <v>1617369000</v>
       </c>
       <c r="O4" t="n">
-        <v>12302000</v>
+        <v>11405000</v>
       </c>
       <c r="P4" t="n">
-        <v>59980000</v>
+        <v>-6916000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1570851000</v>
+        <v>1572570000</v>
       </c>
       <c r="R4" t="n">
-        <v>56081000</v>
+        <v>56691000</v>
       </c>
       <c r="S4" t="n">
-        <v>56081000</v>
+        <v>56691000</v>
       </c>
       <c r="T4" t="n">
-        <v>273482000</v>
+        <v>222292000</v>
       </c>
       <c r="U4" t="n">
-        <v>8461000</v>
+        <v>7565000</v>
       </c>
       <c r="V4" t="n">
-        <v>1929000</v>
+        <v>3252000</v>
       </c>
       <c r="W4" t="n">
-        <v>5175000</v>
+        <v>3374000</v>
       </c>
       <c r="X4" t="n">
-        <v>1357000</v>
+        <v>939000</v>
       </c>
       <c r="Y4" t="n">
-        <v>1357000</v>
+        <v>939000</v>
       </c>
       <c r="Z4" t="n">
-        <v>265021000</v>
+        <v>214727000</v>
       </c>
       <c r="AA4" t="n">
-        <v>23569000</v>
+        <v>23968000</v>
       </c>
       <c r="AB4" t="n">
-        <v>219275000</v>
+        <v>183311000</v>
       </c>
       <c r="AC4" t="n">
-        <v>219275000</v>
+        <v>183311000</v>
       </c>
       <c r="AD4" t="n">
-        <v>2160000</v>
+        <v>2312000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2160000</v>
+        <v>2312000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1959069000</v>
+        <v>1839235000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1455650000</v>
+        <v>1476192000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>439975000</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
+        <v>462449000</v>
+      </c>
+      <c r="AJ4" t="inlineStr"/>
       <c r="AK4" t="n">
-        <v>37604000</v>
+        <v>111878000</v>
       </c>
       <c r="AL4" t="n">
-        <v>402371000</v>
+        <v>350571000</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2049,28 +2051,26 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>865873000</v>
+        <v>837359000</v>
       </c>
       <c r="AP4" t="n">
-        <v>2393000</v>
+        <v>1344000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2393000</v>
+        <v>1344000</v>
       </c>
       <c r="AR4" t="n">
-        <v>140844000</v>
+        <v>138467000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-22425000</v>
+        <v>-26736000</v>
       </c>
       <c r="AT4" t="n">
-        <v>163269000</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
+        <v>165203000</v>
+      </c>
+      <c r="AU4" t="inlineStr"/>
       <c r="AV4" t="n">
-        <v>3572000</v>
+        <v>5506000</v>
       </c>
       <c r="AW4" t="n">
         <v>4306000</v>
@@ -2082,223 +2082,223 @@
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>503419000</v>
+        <v>363043000</v>
       </c>
       <c r="BA4" t="n">
-        <v>164480000</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8305000</v>
-      </c>
+        <v>108205000</v>
+      </c>
+      <c r="BB4" t="inlineStr"/>
       <c r="BC4" t="n">
-        <v>106485000</v>
+        <v>96980000</v>
       </c>
       <c r="BD4" t="n">
-        <v>106485000</v>
+        <v>96980000</v>
       </c>
       <c r="BE4" t="n">
-        <v>8305000</v>
+        <v>3897000</v>
       </c>
       <c r="BF4" t="n">
-        <v>1603000</v>
+        <v>1624000</v>
       </c>
       <c r="BG4" t="n">
-        <v>222546000</v>
+        <v>152337000</v>
       </c>
       <c r="BH4" t="n">
-        <v>9982000</v>
+        <v>8005000</v>
       </c>
       <c r="BI4" t="n">
-        <v>212564000</v>
+        <v>144332000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>134763000</v>
+        <v>129633000</v>
       </c>
       <c r="BK4" t="n">
-        <v>77801000</v>
+        <v>14699000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>560813000</v>
+        <v>566912566</v>
       </c>
       <c r="C5" t="n">
-        <v>560813000</v>
+        <v>566912566</v>
       </c>
       <c r="D5" t="n">
-        <v>51528000</v>
+        <v>62450000</v>
       </c>
       <c r="E5" t="n">
-        <v>234707000</v>
+        <v>292593000</v>
       </c>
       <c r="F5" t="n">
-        <v>1844355000</v>
+        <v>1384245000</v>
       </c>
       <c r="G5" t="n">
-        <v>2080504000</v>
+        <v>1679147000</v>
       </c>
       <c r="H5" t="n">
-        <v>275629000</v>
+        <v>120600000</v>
       </c>
       <c r="I5" t="n">
-        <v>1844355000</v>
+        <v>1384245000</v>
       </c>
       <c r="J5" t="n">
-        <v>1845797000</v>
+        <v>1386554000</v>
       </c>
       <c r="K5" t="n">
-        <v>1857833000</v>
+        <v>1387024000</v>
       </c>
       <c r="L5" t="n">
-        <v>1842469000</v>
+        <v>1385915000</v>
       </c>
       <c r="M5" t="n">
-        <v>-3328000</v>
+        <v>-639000</v>
       </c>
       <c r="N5" t="n">
-        <v>1845797000</v>
+        <v>1386554000</v>
       </c>
       <c r="O5" t="n">
-        <v>11867000</v>
+        <v>11202000</v>
       </c>
       <c r="P5" t="n">
-        <v>195856000</v>
+        <v>-248618000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1570851000</v>
+        <v>1572570000</v>
       </c>
       <c r="R5" t="n">
-        <v>56081000</v>
+        <v>56691000</v>
       </c>
       <c r="S5" t="n">
-        <v>56081000</v>
+        <v>56691000</v>
       </c>
       <c r="T5" t="n">
-        <v>294614000</v>
+        <v>331153000</v>
       </c>
       <c r="U5" t="n">
-        <v>17211000</v>
-      </c>
-      <c r="V5" t="inlineStr"/>
+        <v>5716000</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1656000</v>
+      </c>
       <c r="W5" t="n">
-        <v>5175000</v>
+        <v>3590000</v>
       </c>
       <c r="X5" t="n">
-        <v>12036000</v>
+        <v>470000</v>
       </c>
       <c r="Y5" t="n">
-        <v>12036000</v>
+        <v>470000</v>
       </c>
       <c r="Z5" t="n">
-        <v>277403000</v>
+        <v>325437000</v>
       </c>
       <c r="AA5" t="n">
-        <v>24841000</v>
+        <v>23968000</v>
       </c>
       <c r="AB5" t="n">
-        <v>222671000</v>
+        <v>292123000</v>
       </c>
       <c r="AC5" t="n">
-        <v>222671000</v>
+        <v>292123000</v>
       </c>
       <c r="AD5" t="n">
-        <v>18231000</v>
+        <v>26280000</v>
       </c>
       <c r="AE5" t="n">
-        <v>18231000</v>
+        <v>2312000</v>
       </c>
       <c r="AF5" t="n">
-        <v>2137083000</v>
+        <v>1717068000</v>
       </c>
       <c r="AG5" t="n">
-        <v>1584051000</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>1271031000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>7775000</v>
+      </c>
       <c r="AI5" t="n">
-        <v>443784000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>5373000</v>
-      </c>
+        <v>471139000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
       <c r="AK5" t="n">
-        <v>71981000</v>
+        <v>106924000</v>
       </c>
       <c r="AL5" t="n">
-        <v>366430000</v>
-      </c>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
+        <v>364215000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
       <c r="AO5" t="n">
-        <v>976946000</v>
+        <v>670728000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1442000</v>
+        <v>2309000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1442000</v>
+        <v>2309000</v>
       </c>
       <c r="AR5" t="n">
-        <v>161707000</v>
+        <v>99389000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-17811000</v>
+        <v>-30459000</v>
       </c>
       <c r="AT5" t="n">
-        <v>179518000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>16249000</v>
-      </c>
+        <v>129848000</v>
+      </c>
+      <c r="AU5" t="inlineStr"/>
       <c r="AV5" t="n">
-        <v>3572000</v>
+        <v>6402000</v>
       </c>
       <c r="AW5" t="n">
-        <v>4306000</v>
+        <v>4223000</v>
       </c>
       <c r="AX5" t="n">
-        <v>155391000</v>
+        <v>119223000</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>553032000</v>
+        <v>446037000</v>
       </c>
       <c r="BA5" t="n">
-        <v>201514000</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>6647000</v>
-      </c>
+        <v>106080000</v>
+      </c>
+      <c r="BB5" t="inlineStr"/>
       <c r="BC5" t="n">
-        <v>104894000</v>
+        <v>63910000</v>
       </c>
       <c r="BD5" t="n">
-        <v>104894000</v>
+        <v>63910000</v>
       </c>
       <c r="BE5" t="n">
-        <v>23962000</v>
+        <v>21616000</v>
       </c>
       <c r="BF5" t="n">
-        <v>1121000</v>
+        <v>2219000</v>
       </c>
       <c r="BG5" t="n">
-        <v>221541000</v>
+        <v>252212000</v>
       </c>
       <c r="BH5" t="n">
-        <v>38362000</v>
+        <v>22069000</v>
       </c>
       <c r="BI5" t="n">
-        <v>183179000</v>
+        <v>230143000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>99939000</v>
+        <v>210269000</v>
       </c>
       <c r="BK5" t="n">
-        <v>83240000</v>
+        <v>19874000</v>
       </c>
     </row>
   </sheetData>
@@ -2579,602 +2579,602 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45473</v>
+        <v>44377</v>
       </c>
       <c r="B2" t="n">
-        <v>654000</v>
+        <v>-28962000</v>
       </c>
       <c r="C2" t="n">
-        <v>-67034000</v>
+        <v>-36773000</v>
       </c>
       <c r="D2" t="n">
-        <v>169703000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
+        <v>50426000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2881000</v>
+      </c>
       <c r="F2" t="n">
-        <v>-9189000</v>
+        <v>-18382000</v>
       </c>
       <c r="G2" t="n">
-        <v>110589000</v>
+        <v>183179000</v>
       </c>
       <c r="H2" t="n">
-        <v>82970000</v>
+        <v>123082000</v>
       </c>
       <c r="I2" t="n">
-        <v>-18000</v>
+        <v>4925000</v>
       </c>
       <c r="J2" t="n">
-        <v>27637000</v>
+        <v>55172000</v>
       </c>
       <c r="K2" t="n">
-        <v>102669000</v>
+        <v>16534000</v>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>2881000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>2881000</v>
+      </c>
       <c r="O2" t="n">
-        <v>102669000</v>
+        <v>13653000</v>
       </c>
       <c r="P2" t="n">
-        <v>102669000</v>
+        <v>13653000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-67034000</v>
+        <v>-36773000</v>
       </c>
       <c r="R2" t="n">
-        <v>169703000</v>
+        <v>50426000</v>
       </c>
       <c r="S2" t="n">
-        <v>-84875000</v>
+        <v>49218000</v>
       </c>
       <c r="T2" t="n">
-        <v>2125000</v>
+        <v>23772000</v>
       </c>
       <c r="U2" t="n">
-        <v>2602000</v>
+        <v>364000</v>
       </c>
       <c r="V2" t="n">
-        <v>-80734000</v>
+        <v>-16925000</v>
       </c>
       <c r="W2" t="n">
-        <v>140361000</v>
+        <v>130422000</v>
       </c>
       <c r="X2" t="n">
-        <v>-221095000</v>
+        <v>-147347000</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+        <v>-114000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="n">
+        <v>-114000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8298000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>8298000</v>
+      </c>
       <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
+        <v>-1555000</v>
+      </c>
+      <c r="AE2" t="inlineStr"/>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-1555000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-8868000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>321000</v>
-      </c>
+        <v>-16827000</v>
+      </c>
+      <c r="AH2" t="inlineStr"/>
       <c r="AI2" t="n">
-        <v>-9189000</v>
+        <v>-16827000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>9843000</v>
+        <v>-10580000</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-1950000</v>
       </c>
       <c r="AL2" t="n">
-        <v>17268000</v>
+        <v>11833000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-2134000</v>
+        <v>-2829000</v>
       </c>
       <c r="AN2" t="n">
-        <v>3012000</v>
+        <v>-8871000</v>
       </c>
       <c r="AO2" t="n">
-        <v>302000</v>
+        <v>1413000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-564000</v>
+        <v>2633000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7821000</v>
+        <v>-13102000</v>
       </c>
       <c r="AR2" t="n">
-        <v>-4547000</v>
+        <v>185000</v>
       </c>
       <c r="AS2" t="n">
-        <v>-13356000</v>
+        <v>-11583000</v>
       </c>
       <c r="AT2" t="n">
-        <v>79000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>10743000</v>
-      </c>
+        <v>462000</v>
+      </c>
+      <c r="AU2" t="inlineStr"/>
       <c r="AV2" t="n">
-        <v>4219000</v>
+        <v>4566000</v>
       </c>
       <c r="AW2" t="n">
-        <v>4219000</v>
+        <v>4566000</v>
       </c>
       <c r="AX2" t="n">
-        <v>168776000</v>
+        <v>-21659000</v>
       </c>
       <c r="AY2" t="n">
-        <v>2945000</v>
+        <v>-10014000</v>
       </c>
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="n">
-        <v>-241945000</v>
+        <v>31985000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45107</v>
+        <v>44742</v>
       </c>
       <c r="B3" t="n">
-        <v>-19924000</v>
+        <v>434000</v>
       </c>
       <c r="C3" t="n">
-        <v>-236963000</v>
+        <v>-44975000</v>
       </c>
       <c r="D3" t="n">
-        <v>194004000</v>
+        <v>50462000</v>
       </c>
       <c r="E3" t="n">
+        <v>1867000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-2695000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>77801000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>183179000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-335000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-105043000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-7435000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-14789000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1867000</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1867000</v>
+      </c>
+      <c r="O3" t="n">
+        <v>5487000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5487000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-44975000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>50462000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-100737000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>37034000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>917000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>-146916000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>127552000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>-274468000</v>
+      </c>
+      <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" t="n">
-        <v>-2266000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>82970000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>77801000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-776000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>5945000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-42889000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>70000</v>
-      </c>
-      <c r="M3" t="n">
+      <c r="Z3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="n">
+      <c r="AA3" t="n">
         <v>0</v>
       </c>
-      <c r="O3" t="n">
-        <v>-42959000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>-42959000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>-236963000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>194004000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>66492000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>56275000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>1221000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>-9353000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>141098000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>-150451000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>18976000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>18976000</v>
-      </c>
-      <c r="AA3" t="inlineStr"/>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="n">
-        <v>1605000</v>
+        <v>-2385000</v>
       </c>
       <c r="AE3" t="n">
-        <v>1639000</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-34000</v>
+        <v>-2385000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-2232000</v>
+        <v>-310000</v>
       </c>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="n">
-        <v>-2232000</v>
+        <v>-310000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-17658000</v>
+        <v>3129000</v>
       </c>
       <c r="AK3" t="n">
-        <v>482000</v>
+        <v>-236000</v>
       </c>
       <c r="AL3" t="n">
-        <v>13147000</v>
+        <v>8451000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-3263000</v>
+        <v>-1192000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-21437000</v>
+        <v>1355000</v>
       </c>
       <c r="AO3" t="n">
-        <v>-1690000</v>
+        <v>8419000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1891000</v>
+        <v>-1655000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7573000</v>
+        <v>-4927000</v>
       </c>
       <c r="AR3" t="n">
-        <v>-29211000</v>
+        <v>-482000</v>
       </c>
       <c r="AS3" t="n">
-        <v>-10621000</v>
+        <v>-6091000</v>
       </c>
       <c r="AT3" t="n">
+        <v>435000</v>
+      </c>
+      <c r="AU3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="n">
-        <v>4876000</v>
-      </c>
       <c r="AV3" t="n">
-        <v>4311000</v>
+        <v>4614000</v>
       </c>
       <c r="AW3" t="n">
-        <v>4311000</v>
+        <v>4614000</v>
       </c>
       <c r="AX3" t="n">
-        <v>60991000</v>
+        <v>127336000</v>
       </c>
       <c r="AY3" t="n">
-        <v>505000</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
+        <v>9655000</v>
+      </c>
+      <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="n">
-        <v>-69352000</v>
+        <v>-143517000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44742</v>
+        <v>45107</v>
       </c>
       <c r="B4" t="n">
-        <v>434000</v>
+        <v>-19924000</v>
       </c>
       <c r="C4" t="n">
-        <v>-44975000</v>
+        <v>-236963000</v>
       </c>
       <c r="D4" t="n">
-        <v>50462000</v>
+        <v>194004000</v>
       </c>
       <c r="E4" t="n">
-        <v>1867000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-2695000</v>
+        <v>-2266000</v>
       </c>
       <c r="G4" t="n">
+        <v>82970000</v>
+      </c>
+      <c r="H4" t="n">
         <v>77801000</v>
       </c>
-      <c r="H4" t="n">
-        <v>183179000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-335000</v>
+        <v>-776000</v>
       </c>
       <c r="J4" t="n">
-        <v>-105043000</v>
+        <v>5945000</v>
       </c>
       <c r="K4" t="n">
-        <v>-7435000</v>
+        <v>-42889000</v>
       </c>
       <c r="L4" t="n">
-        <v>-14789000</v>
+        <v>70000</v>
       </c>
       <c r="M4" t="n">
-        <v>1867000</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>1867000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>5487000</v>
+        <v>-42959000</v>
       </c>
       <c r="P4" t="n">
-        <v>5487000</v>
+        <v>-42959000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-44975000</v>
+        <v>-236963000</v>
       </c>
       <c r="R4" t="n">
-        <v>50462000</v>
+        <v>194004000</v>
       </c>
       <c r="S4" t="n">
-        <v>-100737000</v>
+        <v>66492000</v>
       </c>
       <c r="T4" t="n">
-        <v>37034000</v>
+        <v>56275000</v>
       </c>
       <c r="U4" t="n">
-        <v>917000</v>
+        <v>1221000</v>
       </c>
       <c r="V4" t="n">
-        <v>-146916000</v>
+        <v>-9353000</v>
       </c>
       <c r="W4" t="n">
-        <v>127552000</v>
+        <v>141098000</v>
       </c>
       <c r="X4" t="n">
-        <v>-274468000</v>
+        <v>-150451000</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>18976000</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
+        <v>18976000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="n">
-        <v>-2385000</v>
+        <v>1605000</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1639000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2385000</v>
+        <v>-34000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-310000</v>
+        <v>-2232000</v>
       </c>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="n">
-        <v>-310000</v>
+        <v>-2232000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3129000</v>
+        <v>-17658000</v>
       </c>
       <c r="AK4" t="n">
-        <v>-236000</v>
+        <v>482000</v>
       </c>
       <c r="AL4" t="n">
-        <v>8451000</v>
+        <v>13147000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1192000</v>
+        <v>-3263000</v>
       </c>
       <c r="AN4" t="n">
-        <v>1355000</v>
+        <v>-21437000</v>
       </c>
       <c r="AO4" t="n">
-        <v>8419000</v>
+        <v>-1690000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1655000</v>
+        <v>1891000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-4927000</v>
+        <v>7573000</v>
       </c>
       <c r="AR4" t="n">
-        <v>-482000</v>
+        <v>-29211000</v>
       </c>
       <c r="AS4" t="n">
-        <v>-6091000</v>
+        <v>-10621000</v>
       </c>
       <c r="AT4" t="n">
-        <v>435000</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
+        <v>4876000</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4311000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4311000</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>60991000</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>505000</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>0</v>
       </c>
-      <c r="AV4" t="n">
-        <v>4614000</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>4614000</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>127336000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>9655000</v>
-      </c>
-      <c r="AZ4" t="inlineStr"/>
       <c r="BA4" t="n">
-        <v>-143517000</v>
+        <v>-69352000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44377</v>
+        <v>45473</v>
       </c>
       <c r="B5" t="n">
-        <v>-28962000</v>
+        <v>654000</v>
       </c>
       <c r="C5" t="n">
-        <v>-36773000</v>
+        <v>-67034000</v>
       </c>
       <c r="D5" t="n">
-        <v>50426000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2881000</v>
-      </c>
+        <v>169703000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>-18382000</v>
+        <v>-9189000</v>
       </c>
       <c r="G5" t="n">
-        <v>183179000</v>
+        <v>110589000</v>
       </c>
       <c r="H5" t="n">
-        <v>123082000</v>
+        <v>82970000</v>
       </c>
       <c r="I5" t="n">
-        <v>4925000</v>
+        <v>-18000</v>
       </c>
       <c r="J5" t="n">
-        <v>55172000</v>
+        <v>27637000</v>
       </c>
       <c r="K5" t="n">
-        <v>16534000</v>
+        <v>102669000</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="n">
-        <v>2881000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2881000</v>
-      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>13653000</v>
+        <v>102669000</v>
       </c>
       <c r="P5" t="n">
-        <v>13653000</v>
+        <v>102669000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-36773000</v>
+        <v>-67034000</v>
       </c>
       <c r="R5" t="n">
-        <v>50426000</v>
+        <v>169703000</v>
       </c>
       <c r="S5" t="n">
-        <v>49218000</v>
+        <v>-84875000</v>
       </c>
       <c r="T5" t="n">
-        <v>23772000</v>
+        <v>2125000</v>
       </c>
       <c r="U5" t="n">
-        <v>364000</v>
+        <v>2602000</v>
       </c>
       <c r="V5" t="n">
-        <v>-16925000</v>
+        <v>-80734000</v>
       </c>
       <c r="W5" t="n">
-        <v>130422000</v>
+        <v>140361000</v>
       </c>
       <c r="X5" t="n">
-        <v>-147347000</v>
+        <v>-221095000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-114000</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="n">
-        <v>-114000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>8298000</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>8298000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="n">
-        <v>-1555000</v>
-      </c>
-      <c r="AE5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
       <c r="AF5" t="n">
-        <v>-1555000</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>-16827000</v>
-      </c>
-      <c r="AH5" t="inlineStr"/>
+        <v>-8868000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>321000</v>
+      </c>
       <c r="AI5" t="n">
-        <v>-16827000</v>
+        <v>-9189000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-10580000</v>
+        <v>9843000</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1950000</v>
+        <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>11833000</v>
+        <v>17268000</v>
       </c>
       <c r="AM5" t="n">
-        <v>-2829000</v>
+        <v>-2134000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-8871000</v>
+        <v>3012000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1413000</v>
+        <v>302000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2633000</v>
+        <v>-564000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-13102000</v>
+        <v>7821000</v>
       </c>
       <c r="AR5" t="n">
-        <v>185000</v>
+        <v>-4547000</v>
       </c>
       <c r="AS5" t="n">
-        <v>-11583000</v>
+        <v>-13356000</v>
       </c>
       <c r="AT5" t="n">
-        <v>462000</v>
-      </c>
-      <c r="AU5" t="inlineStr"/>
+        <v>79000</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>10743000</v>
+      </c>
       <c r="AV5" t="n">
-        <v>4566000</v>
+        <v>4219000</v>
       </c>
       <c r="AW5" t="n">
-        <v>4566000</v>
+        <v>4219000</v>
       </c>
       <c r="AX5" t="n">
-        <v>-21659000</v>
+        <v>168776000</v>
       </c>
       <c r="AY5" t="n">
-        <v>-10014000</v>
+        <v>2945000</v>
       </c>
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="n">
-        <v>31985000</v>
+        <v>-241945000</v>
       </c>
     </row>
   </sheetData>
@@ -3714,187 +3714,187 @@
       </c>
       <c r="DA1" t="inlineStr">
         <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DU1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3997,28 +3997,28 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="V2" t="n">
-        <v>0.147</v>
+        <v>0.145</v>
       </c>
       <c r="W2" t="n">
         <v>0.143</v>
       </c>
       <c r="X2" t="n">
-        <v>0.147</v>
+        <v>0.145</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.147</v>
+        <v>0.149</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.147</v>
+        <v>0.145</v>
       </c>
       <c r="AA2" t="n">
         <v>0.143</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.147</v>
+        <v>0.145</v>
       </c>
       <c r="AC2" t="n">
         <v>1543968000</v>
@@ -4027,28 +4027,28 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.287</v>
+        <v>0.303</v>
       </c>
       <c r="AF2" t="n">
-        <v>16000</v>
+        <v>133600</v>
       </c>
       <c r="AG2" t="n">
-        <v>16000</v>
+        <v>133600</v>
       </c>
       <c r="AH2" t="n">
-        <v>62133</v>
+        <v>50386</v>
       </c>
       <c r="AI2" t="n">
-        <v>16000</v>
+        <v>13600</v>
       </c>
       <c r="AJ2" t="n">
-        <v>16000</v>
+        <v>13600</v>
       </c>
       <c r="AK2" t="n">
         <v>0.144</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.153</v>
+        <v>0.152</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -4060,13 +4060,13 @@
         <v>81068504</v>
       </c>
       <c r="AP2" t="n">
-        <v>83336147</v>
+        <v>84469972</v>
       </c>
       <c r="AQ2" t="n">
         <v>0.131</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.345</v>
+        <v>0.325</v>
       </c>
       <c r="AS2" t="n">
         <v>16.4</v>
@@ -4078,10 +4078,10 @@
         <v>1.0829493</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.15008</v>
+        <v>0.15066</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.16781</v>
+        <v>0.164785</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
         <v>-48959000</v>
       </c>
       <c r="BO2" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -4154,10 +4154,10 @@
         <v>-27.178</v>
       </c>
       <c r="BT2" t="n">
-        <v>-0.5476923</v>
+        <v>-0.40399998</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.018</v>
@@ -4270,140 +4270,140 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DA2" t="n">
-        <v>-0.024809986</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>-0.1478457</v>
-      </c>
-      <c r="DC2" t="n">
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>WINFULL GP</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>Winfull Group Holdings Limited</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>-0.0076599866</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>-0.05084287</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>-0.021784991</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>-0.13220252</v>
+      </c>
+      <c r="DI2" t="n">
         <v>15</v>
       </c>
-      <c r="DD2" t="n">
+      <c r="DJ2" t="n">
         <v>15</v>
       </c>
-      <c r="DE2" t="b">
+      <c r="DK2" t="n">
+        <v>1782112727</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>HKG</t>
+        </is>
+      </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>finmb_7658032</t>
+        </is>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DR2" t="b">
         <v>0</v>
       </c>
-      <c r="DF2" t="b">
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-4.0268435</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="DV2" t="b">
         <v>0</v>
       </c>
-      <c r="DG2" t="n">
+      <c r="DW2" t="n">
         <v>1021944600000</v>
       </c>
-      <c r="DH2" t="n">
-        <v>-0.003999993</v>
-      </c>
-      <c r="DI2" t="inlineStr">
-        <is>
-          <t>0.143 - 0.147</t>
-        </is>
-      </c>
-      <c r="DJ2" t="inlineStr">
+      <c r="DX2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-0.0059999973</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>0.143 - 0.145</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>HKSE</t>
         </is>
       </c>
-      <c r="DK2" t="n">
-        <v>62133</v>
-      </c>
-      <c r="DL2" t="n">
+      <c r="EB2" t="n">
+        <v>50386</v>
+      </c>
+      <c r="EC2" t="n">
         <v>0.012000009</v>
       </c>
-      <c r="DM2" t="n">
+      <c r="ED2" t="n">
         <v>0.09160313</v>
       </c>
-      <c r="DN2" t="inlineStr">
-        <is>
-          <t>0.131 - 0.345</t>
-        </is>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.20199999</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.5855072</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>-54.76923</v>
-      </c>
-      <c r="DR2" t="n">
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>0.131 - 0.325</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>-0.18199998</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.55999994</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-40.399998</v>
+      </c>
+      <c r="EI2" t="n">
         <v>1740405466</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EJ2" t="n">
         <v>1740405466</v>
       </c>
-      <c r="DT2" t="b">
+      <c r="EK2" t="b">
         <v>0</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.0070799887</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.047174767</v>
-      </c>
-      <c r="DX2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="DY2" t="n">
-        <v>1780381362</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
-        <is>
-          <t>WINFULL GP</t>
-        </is>
-      </c>
-      <c r="EA2" t="inlineStr">
-        <is>
-          <t>Winfull Group Holdings Limited</t>
-        </is>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>finmb_7658032</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EJ2" t="n">
-        <v>-2.7210836</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>0.143</v>
       </c>
       <c r="EL2" t="inlineStr"/>
     </row>
